--- a/membership_application_form_templates/018_nurses_welfare_member_039_s_registration_form--membership_application_form_templates.xlsx
+++ b/membership_application_form_templates/018_nurses_welfare_member_039_s_registration_form--membership_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Address List Page</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -881,12 +881,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_license_number_page</t>
+          <t>medical_license_number_page_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical License Number</t>
+          <t>Medical License Number Page 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>medical_license_number_page</t>
+          <t>medical_license_number_page_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Medical License Number</t>
+          <t>Medical License Number Page 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>membership_status_page</t>
+          <t>membership_status_page_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Membership Status</t>
+          <t>Membership Status Page 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Work'}</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'md'}</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'MD'}</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'rn'}</t>
+          <t>rn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'RN'}</t>
+          <t>RN</t>
         </is>
       </c>
     </row>
@@ -1270,63 +1270,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'np'}</t>
+          <t>np</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'NP'}</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>membership_status_page_choices</t>
+          <t>membership_status_page_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>membership_status_page_choices</t>
+          <t>membership_status_page_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>membership_status_page_choices</t>
+          <t>membership_status_page_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
